--- a/kd_advanced_with_charts.xlsx
+++ b/kd_advanced_with_charts.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11122"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/burakcimen/Desktop/DSA 210/DSA Proje Dosyaları/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026DDA15-7DEA-C545-82A1-B29726144E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="AdvancedStats" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -36,6 +30,9 @@
   </si>
   <si>
     <t>MPG</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
   </si>
   <si>
     <t>Period</t>
@@ -62,8 +59,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,30 +123,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -167,14 +146,12 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -245,7 +222,7 @@
                   <c:v>63.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65.099999999999994</c:v>
+                  <c:v>65.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>64</c:v>
@@ -254,7 +231,7 @@
                   <c:v>63.1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66.599999999999994</c:v>
+                  <c:v>66.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>63.4</c:v>
@@ -274,22 +251,8 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0E12-C945-90A0-598D2A7E8CAA}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
+        <c:marker val="1"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:lineChart>
@@ -298,7 +261,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -316,25 +278,21 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -353,11 +311,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -365,8 +321,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -377,18 +331,8 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -406,14 +350,12 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -513,22 +455,8 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B109-F04D-82E0-6AFC256058B4}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
+        <c:marker val="1"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:lineChart>
@@ -537,7 +465,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -555,25 +482,21 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -592,11 +515,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -604,8 +525,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -616,18 +535,8 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -645,14 +554,12 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -752,22 +659,8 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3052-2F4A-9A2B-8FA7A5B7ACCB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
+        <c:marker val="1"/>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:lineChart>
@@ -776,7 +669,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -794,25 +686,21 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -831,11 +719,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -843,8 +729,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -855,18 +739,8 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -884,14 +758,12 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -956,16 +828,16 @@
                   <c:v>38.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>33.799999999999997</c:v>
+                  <c:v>33.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.799999999999997</c:v>
+                  <c:v>35.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>33.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34.200000000000003</c:v>
+                  <c:v>34.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>34.6</c:v>
@@ -974,13 +846,13 @@
                   <c:v>33.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>37.200000000000003</c:v>
+                  <c:v>37.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>35.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>37.200000000000003</c:v>
+                  <c:v>37.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>36.5</c:v>
@@ -991,22 +863,8 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4662-7C4C-86EC-2B2875269084}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
+        <c:marker val="1"/>
         <c:axId val="50040001"/>
         <c:axId val="50040002"/>
       </c:lineChart>
@@ -1015,7 +873,6 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1033,25 +890,21 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040002"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1070,11 +923,9 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="0"/>
+          <c:layout/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -1082,8 +933,6 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1097,26 +946,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>558800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1133,26 +976,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1169,26 +1006,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1205,26 +1036,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1243,9 +1068,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1283,7 +1108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1317,7 +1142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1352,10 +1176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1528,11 +1351,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1551,8 +1374,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>2013</v>
       </c>
@@ -1568,11 +1394,11 @@
       <c r="E2">
         <v>38.5</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2014</v>
       </c>
@@ -1586,13 +1412,13 @@
         <v>104.9</v>
       </c>
       <c r="E3">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
+        <v>33.8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>2015</v>
       </c>
@@ -1606,18 +1432,18 @@
         <v>103.7</v>
       </c>
       <c r="E4">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
+        <v>35.8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>2016</v>
       </c>
       <c r="B5">
-        <v>65.099999999999994</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -1628,11 +1454,11 @@
       <c r="E5">
         <v>33.4</v>
       </c>
-      <c r="F5" t="s">
-        <v>6</v>
+      <c r="G5" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>2017</v>
       </c>
@@ -1646,13 +1472,13 @@
         <v>106.6</v>
       </c>
       <c r="E6">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="F6" t="s">
-        <v>6</v>
+        <v>34.2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>2018</v>
       </c>
@@ -1668,16 +1494,16 @@
       <c r="E7">
         <v>34.6</v>
       </c>
-      <c r="F7" t="s">
-        <v>6</v>
+      <c r="G7" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>2020</v>
       </c>
       <c r="B8">
-        <v>66.599999999999994</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C8">
         <v>30.8</v>
@@ -1688,11 +1514,11 @@
       <c r="E8">
         <v>33.1</v>
       </c>
-      <c r="F8" t="s">
-        <v>7</v>
+      <c r="G8" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>2021</v>
       </c>
@@ -1706,13 +1532,13 @@
         <v>112.3</v>
       </c>
       <c r="E9">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
+        <v>37.2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2022</v>
       </c>
@@ -1728,11 +1554,11 @@
       <c r="E10">
         <v>35.6</v>
       </c>
-      <c r="F10" t="s">
-        <v>7</v>
+      <c r="G10" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2023</v>
       </c>
@@ -1746,13 +1572,13 @@
         <v>114.4</v>
       </c>
       <c r="E11">
-        <v>37.200000000000003</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
+        <v>37.2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2024</v>
       </c>
@@ -1768,11 +1594,11 @@
       <c r="E12">
         <v>36.5</v>
       </c>
-      <c r="F12" t="s">
-        <v>7</v>
+      <c r="G12" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2025</v>
       </c>
@@ -1788,8 +1614,8 @@
       <c r="E13">
         <v>36.1</v>
       </c>
-      <c r="F13" t="s">
-        <v>7</v>
+      <c r="G13" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1799,39 +1625,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>63.733333333333327</v>
+        <v>63.73333333333333</v>
       </c>
       <c r="C2">
-        <v>64.266666666666666</v>
+        <v>64.26666666666667</v>
       </c>
       <c r="D2">
-        <v>0.53333333333333854</v>
+        <v>0.5333333333333385</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1839,13 +1665,13 @@
         <v>28.93333333333333</v>
       </c>
       <c r="C3">
-        <v>29.216666666666669</v>
+        <v>29.21666666666667</v>
       </c>
       <c r="D3">
-        <v>0.28333333333333499</v>
+        <v>0.283333333333335</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1853,24 +1679,24 @@
         <v>104.9666666666667</v>
       </c>
       <c r="C4">
-        <v>114.18333333333329</v>
+        <v>114.1833333333333</v>
       </c>
       <c r="D4">
-        <v>9.2166666666666828</v>
+        <v>9.216666666666683</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35.049999999999997</v>
+        <v>35.05</v>
       </c>
       <c r="C5">
-        <v>35.950000000000003</v>
+        <v>35.95</v>
       </c>
       <c r="D5">
-        <v>0.90000000000000568</v>
+        <v>0.9000000000000057</v>
       </c>
     </row>
   </sheetData>
